--- a/camp_registration_forms/028_religious_reunion_registration_form--camp_registration_forms.xlsx
+++ b/camp_registration_forms/028_religious_reunion_registration_form--camp_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'mary'}</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Mary'}</t>
+          <t>Mary</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'alice'}</t>
+          <t>alice</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Alice'}</t>
+          <t>Alice</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'dave'}</t>
+          <t>dave</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Dave'}</t>
+          <t>Dave</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'mary'}</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Mary'}</t>
+          <t>Mary</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'alice'}</t>
+          <t>alice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'Alice'}</t>
+          <t>Alice</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'dave'}</t>
+          <t>dave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'Dave'}</t>
+          <t>Dave</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_36,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 36, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_37,_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 37, 'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'mary'}</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Mary'}</t>
+          <t>Mary</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_44,_'label':_'alice'}</t>
+          <t>alice</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 44, 'label': 'Alice'}</t>
+          <t>Alice</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_45,_'label':_'dave'}</t>
+          <t>dave</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 45, 'label': 'Dave'}</t>
+          <t>Dave</t>
         </is>
       </c>
     </row>
